--- a/artfynd/A 29376-2022 artfynd.xlsx
+++ b/artfynd/A 29376-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29376-2022 artfynd.xlsx
+++ b/artfynd/A 29376-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80757104</v>
+        <v>80757005</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hallsjöbäcken söder om, Vg</t>
+          <t>Hallsjön NV, väster om vägen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>350077.4551600465</v>
+        <v>350140</v>
       </c>
       <c r="R2" t="n">
-        <v>6473655.348818466</v>
+        <v>6473733</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2019-05-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-05-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,6 +774,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>80757104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hallsjöbäcken söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>350077</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6473655</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västra Tunhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-05-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-05-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Barrskogar, blandskog, myr och tallmossar</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
